--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_brokerage_investment_banking.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0636</v>
+        <v>0.09695000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.0452</v>
+        <v>0.163</v>
       </c>
       <c r="G2">
-        <v>0.08569353667392882</v>
+        <v>0.05998868138087153</v>
       </c>
       <c r="H2">
-        <v>0.08569353667392882</v>
+        <v>0.05998868138087153</v>
       </c>
       <c r="I2">
-        <v>0.03282498184458969</v>
+        <v>0.07017543859649122</v>
       </c>
       <c r="J2">
-        <v>0.03282498184458969</v>
+        <v>0.05588173850903846</v>
       </c>
       <c r="K2">
-        <v>-1.034</v>
+        <v>3.572</v>
       </c>
       <c r="L2">
-        <v>-0.1501815541031227</v>
+        <v>0.2021505376344086</v>
       </c>
       <c r="M2">
-        <v>2.749</v>
+        <v>0.413</v>
       </c>
       <c r="N2">
-        <v>0.06826421653836602</v>
+        <v>0.006988155668358713</v>
       </c>
       <c r="O2">
-        <v>-2.658607350096712</v>
+        <v>0.1156215005599104</v>
       </c>
       <c r="P2">
-        <v>2.749</v>
+        <v>0.413</v>
       </c>
       <c r="Q2">
-        <v>0.06826421653836602</v>
+        <v>0.006988155668358713</v>
       </c>
       <c r="R2">
-        <v>-2.658607350096712</v>
+        <v>0.1156215005599104</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.973</v>
+        <v>0.7939999999999999</v>
       </c>
       <c r="V2">
-        <v>0.02416190712689347</v>
+        <v>0.01343485617597293</v>
       </c>
       <c r="W2">
-        <v>-0.006428571428571429</v>
+        <v>0.115609756097561</v>
       </c>
       <c r="X2">
-        <v>0.168003711198444</v>
+        <v>0.3149280799441698</v>
       </c>
       <c r="Y2">
-        <v>-0.1744322826270154</v>
+        <v>-0.1993183238466089</v>
       </c>
       <c r="Z2">
-        <v>0.0439284893959115</v>
+        <v>0.1670321775626725</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1094434924126458</v>
+        <v>0.2137963102512679</v>
       </c>
       <c r="AC2">
-        <v>-0.1094434924126458</v>
+        <v>-0.2137963102512679</v>
       </c>
       <c r="AD2">
-        <v>85.59</v>
+        <v>144.22</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>85.59</v>
+        <v>144.22</v>
       </c>
       <c r="AG2">
-        <v>84.617</v>
+        <v>143.426</v>
       </c>
       <c r="AH2">
-        <v>0.680041315747656</v>
+        <v>0.7093252016525674</v>
       </c>
       <c r="AI2">
-        <v>0.7257695242940727</v>
+        <v>0.8594243489660925</v>
       </c>
       <c r="AJ2">
-        <v>0.6775485038474781</v>
+        <v>0.7081856156740369</v>
       </c>
       <c r="AK2">
-        <v>0.7234881195653103</v>
+        <v>0.8587560473248071</v>
       </c>
       <c r="AL2">
-        <v>0.304</v>
+        <v>0.367</v>
       </c>
       <c r="AM2">
-        <v>0.279</v>
+        <v>0.347</v>
       </c>
       <c r="AN2">
-        <v>137.6045016077171</v>
+        <v>100.1527777777778</v>
       </c>
       <c r="AO2">
-        <v>0.743421052631579</v>
+        <v>3.37874659400545</v>
       </c>
       <c r="AP2">
-        <v>136.040192926045</v>
+        <v>99.60138888888888</v>
       </c>
       <c r="AQ2">
-        <v>0.8100358422939069</v>
+        <v>3.573487031700288</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0308</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.0452</v>
+        <v>0.215</v>
       </c>
       <c r="G3">
-        <v>0.1855345911949685</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="H3">
-        <v>0.1855345911949685</v>
+        <v>0.3955223880597015</v>
       </c>
       <c r="I3">
-        <v>0.07106918238993711</v>
+        <v>0.4626865671641791</v>
       </c>
       <c r="J3">
-        <v>0.07106918238993711</v>
+        <v>0.3123903762782539</v>
       </c>
       <c r="K3">
-        <v>0.08</v>
+        <v>0.609</v>
       </c>
       <c r="L3">
-        <v>0.02515723270440251</v>
+        <v>0.2272388059701492</v>
       </c>
       <c r="M3">
-        <v>0.169</v>
+        <v>0.413</v>
       </c>
       <c r="N3">
-        <v>0.04121951219512196</v>
+        <v>0.1424137931034483</v>
       </c>
       <c r="O3">
-        <v>2.1125</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="P3">
-        <v>0.169</v>
+        <v>0.413</v>
       </c>
       <c r="Q3">
-        <v>0.04121951219512196</v>
+        <v>0.1424137931034483</v>
       </c>
       <c r="R3">
-        <v>2.1125</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.485</v>
+        <v>0.577</v>
       </c>
       <c r="V3">
-        <v>0.1182926829268293</v>
+        <v>0.1989655172413793</v>
       </c>
       <c r="W3">
-        <v>0.01680672268907563</v>
+        <v>0.1315334773218143</v>
       </c>
       <c r="X3">
-        <v>0.120294484651001</v>
+        <v>0.2405668693711429</v>
       </c>
       <c r="Y3">
-        <v>-0.1034877619619254</v>
+        <v>-0.1090333920493287</v>
       </c>
       <c r="Z3">
-        <v>0.377627360171001</v>
+        <v>0.3177237700059277</v>
       </c>
       <c r="AA3">
-        <v>0.02683766773542334</v>
+        <v>0.09925384806469716</v>
       </c>
       <c r="AB3">
-        <v>0.09762780007702535</v>
+        <v>0.2013766261691633</v>
       </c>
       <c r="AC3">
-        <v>-0.070790132341602</v>
+        <v>-0.1021227781044661</v>
       </c>
       <c r="AD3">
-        <v>4.29</v>
+        <v>2.52</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.29</v>
+        <v>2.52</v>
       </c>
       <c r="AG3">
-        <v>3.805</v>
+        <v>1.943</v>
       </c>
       <c r="AH3">
-        <v>0.5113230035756853</v>
+        <v>0.4649446494464945</v>
       </c>
       <c r="AI3">
-        <v>0.4809417040358744</v>
+        <v>0.4874274661508704</v>
       </c>
       <c r="AJ3">
-        <v>0.4813409234661607</v>
+        <v>0.4011976047904192</v>
       </c>
       <c r="AK3">
-        <v>0.4510966212211026</v>
+        <v>0.4230350533420423</v>
       </c>
       <c r="AL3">
-        <v>0.304</v>
+        <v>0.367</v>
       </c>
       <c r="AM3">
-        <v>0.279</v>
+        <v>0.347</v>
       </c>
       <c r="AN3">
-        <v>6.897106109324759</v>
+        <v>1.75</v>
       </c>
       <c r="AO3">
-        <v>0.743421052631579</v>
+        <v>3.37874659400545</v>
       </c>
       <c r="AP3">
-        <v>6.117363344051447</v>
+        <v>1.349305555555556</v>
       </c>
       <c r="AQ3">
-        <v>0.8100358422939069</v>
+        <v>3.573487031700288</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Capital Treasuries PLC (COSE:FCT.N0000)</t>
+          <t>Capital Alliance PLC (COSE:CALT.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,9 +855,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.158</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -871,85 +868,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-0.162</v>
+        <v>0.593</v>
       </c>
       <c r="L4">
-        <v>-0.0375</v>
+        <v>0.2837320574162679</v>
       </c>
       <c r="M4">
-        <v>2.58</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.08431372549019607</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-15.92592592592593</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>2.58</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.08431372549019607</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>-15.92592592592593</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0.047</v>
+        <v>0.148</v>
       </c>
       <c r="V4">
-        <v>0.001535947712418301</v>
+        <v>0.008314606741573033</v>
       </c>
       <c r="W4">
-        <v>-0.006428571428571429</v>
+        <v>0.04900826446280992</v>
       </c>
       <c r="X4">
-        <v>0.168003711198444</v>
+        <v>0.3149280799441698</v>
       </c>
       <c r="Y4">
-        <v>-0.1744322826270154</v>
+        <v>-0.2659198154813599</v>
       </c>
       <c r="Z4">
-        <v>0.03311588259193107</v>
+        <v>0.1727272727272727</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1094434924126458</v>
+        <v>0.2137963102512679</v>
       </c>
       <c r="AC4">
-        <v>-0.1094434924126458</v>
+        <v>-0.2137963102512679</v>
       </c>
       <c r="AD4">
-        <v>64.8</v>
+        <v>29.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>64.8</v>
+        <v>29.8</v>
       </c>
       <c r="AG4">
-        <v>64.753</v>
+        <v>29.652</v>
       </c>
       <c r="AH4">
-        <v>0.6792452830188679</v>
+        <v>0.6260504201680672</v>
       </c>
       <c r="AI4">
-        <v>0.7596717467760844</v>
+        <v>0.7813319349764027</v>
       </c>
       <c r="AJ4">
-        <v>0.6790871813157425</v>
+        <v>0.624884093399646</v>
       </c>
       <c r="AK4">
-        <v>0.7595392537506012</v>
+        <v>0.7804801010739102</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -966,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Asia Capital PLC (COSE:ACAP.N0000)</t>
+          <t>First Capital Treasuries PLC (COSE:FCT.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -974,23 +968,29 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.135</v>
+      </c>
+      <c r="E5">
+        <v>0.111</v>
+      </c>
       <c r="G5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.952</v>
+        <v>2.37</v>
       </c>
       <c r="L5">
-        <v>1.547967479674797</v>
+        <v>0.1837209302325581</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -999,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1008,61 +1008,61 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.441</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V5">
-        <v>0.07917414721723519</v>
+        <v>0.001796875</v>
       </c>
       <c r="W5">
-        <v>-0.2441025641025641</v>
+        <v>0.115609756097561</v>
       </c>
       <c r="X5">
-        <v>0.205619163295353</v>
+        <v>0.4294360183079588</v>
       </c>
       <c r="Y5">
-        <v>-0.449721727397917</v>
+        <v>-0.3138262622103978</v>
       </c>
       <c r="Z5">
-        <v>-0.03443449048152296</v>
+        <v>0.1513143232496217</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1113107731219425</v>
+        <v>0.226065939175459</v>
       </c>
       <c r="AC5">
-        <v>-0.1113107731219425</v>
+        <v>-0.226065939175459</v>
       </c>
       <c r="AD5">
-        <v>16.5</v>
+        <v>111.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>16.5</v>
+        <v>111.9</v>
       </c>
       <c r="AG5">
-        <v>16.059</v>
+        <v>111.831</v>
       </c>
       <c r="AH5">
-        <v>0.7476212052560036</v>
+        <v>0.7445109780439122</v>
       </c>
       <c r="AI5">
-        <v>0.6959088991986503</v>
+        <v>0.8987951807228917</v>
       </c>
       <c r="AJ5">
-        <v>0.7424753802764806</v>
+        <v>0.744393633803942</v>
       </c>
       <c r="AK5">
-        <v>0.6901456873952468</v>
+        <v>0.8987390602020398</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_brokerage_investment_banking.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09695000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="E2">
-        <v>0.163</v>
+        <v>0.3845000000000001</v>
       </c>
       <c r="G2">
-        <v>0.05998868138087153</v>
+        <v>0.01426743442098528</v>
       </c>
       <c r="H2">
-        <v>0.05998868138087153</v>
+        <v>0.01426743442098528</v>
       </c>
       <c r="I2">
-        <v>0.07017543859649122</v>
+        <v>0.01298784388995521</v>
       </c>
       <c r="J2">
-        <v>0.05588173850903846</v>
+        <v>0.008706739015934061</v>
       </c>
       <c r="K2">
-        <v>3.572</v>
+        <v>82.23</v>
       </c>
       <c r="L2">
-        <v>0.2021505376344086</v>
+        <v>0.5261036468330135</v>
       </c>
       <c r="M2">
-        <v>0.413</v>
+        <v>6.242</v>
       </c>
       <c r="N2">
-        <v>0.006988155668358713</v>
+        <v>0.05933460076045627</v>
       </c>
       <c r="O2">
-        <v>0.1156215005599104</v>
+        <v>0.07590903563176456</v>
       </c>
       <c r="P2">
-        <v>0.413</v>
+        <v>6.242</v>
       </c>
       <c r="Q2">
-        <v>0.006988155668358713</v>
+        <v>0.05933460076045627</v>
       </c>
       <c r="R2">
-        <v>0.1156215005599104</v>
+        <v>0.07590903563176456</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.7939999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="V2">
-        <v>0.01343485617597293</v>
+        <v>0.007766159695817489</v>
       </c>
       <c r="W2">
-        <v>0.115609756097561</v>
+        <v>2.706349206349207</v>
       </c>
       <c r="X2">
-        <v>0.3149280799441698</v>
+        <v>0.2924792772647096</v>
       </c>
       <c r="Y2">
-        <v>-0.1993183238466089</v>
+        <v>2.413869929084497</v>
       </c>
       <c r="Z2">
-        <v>0.1670321775626725</v>
+        <v>0.935838482540595</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.2137963102512679</v>
+        <v>0.1814665386373609</v>
       </c>
       <c r="AC2">
-        <v>-0.2137963102512679</v>
+        <v>-0.1814665386373609</v>
       </c>
       <c r="AD2">
-        <v>144.22</v>
+        <v>267.86</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>144.22</v>
+        <v>267.86</v>
       </c>
       <c r="AG2">
-        <v>143.426</v>
+        <v>267.043</v>
       </c>
       <c r="AH2">
-        <v>0.7093252016525674</v>
+        <v>0.7180078271591701</v>
       </c>
       <c r="AI2">
-        <v>0.8594243489660925</v>
+        <v>0.7218000538938292</v>
       </c>
       <c r="AJ2">
-        <v>0.7081856156740369</v>
+        <v>0.7173889099324904</v>
       </c>
       <c r="AK2">
-        <v>0.8587560473248071</v>
+        <v>0.7211862278311454</v>
       </c>
       <c r="AL2">
-        <v>0.367</v>
+        <v>1.03</v>
       </c>
       <c r="AM2">
-        <v>0.347</v>
+        <v>0.974</v>
       </c>
       <c r="AN2">
-        <v>100.1527777777778</v>
+        <v>117.4824561403509</v>
       </c>
       <c r="AO2">
-        <v>3.37874659400545</v>
+        <v>1.970873786407767</v>
       </c>
       <c r="AP2">
-        <v>99.60138888888888</v>
+        <v>117.1241228070176</v>
       </c>
       <c r="AQ2">
-        <v>3.573487031700288</v>
+        <v>2.084188911704312</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05889999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="E3">
-        <v>0.215</v>
+        <v>0.192</v>
       </c>
       <c r="G3">
-        <v>0.3955223880597015</v>
+        <v>0.5186046511627908</v>
       </c>
       <c r="H3">
-        <v>0.3955223880597015</v>
+        <v>0.5186046511627908</v>
       </c>
       <c r="I3">
-        <v>0.4626865671641791</v>
+        <v>0.4720930232558139</v>
       </c>
       <c r="J3">
-        <v>0.3123903762782539</v>
+        <v>0.2873412343470483</v>
       </c>
       <c r="K3">
-        <v>0.609</v>
+        <v>0.63</v>
       </c>
       <c r="L3">
-        <v>0.2272388059701492</v>
+        <v>0.1465116279069767</v>
       </c>
       <c r="M3">
-        <v>0.413</v>
+        <v>0.282</v>
       </c>
       <c r="N3">
-        <v>0.1424137931034483</v>
+        <v>0.08545454545454545</v>
       </c>
       <c r="O3">
-        <v>0.6781609195402298</v>
+        <v>0.4476190476190476</v>
       </c>
       <c r="P3">
-        <v>0.413</v>
+        <v>0.282</v>
       </c>
       <c r="Q3">
-        <v>0.1424137931034483</v>
+        <v>0.08545454545454545</v>
       </c>
       <c r="R3">
-        <v>0.6781609195402298</v>
+        <v>0.4476190476190476</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.577</v>
+        <v>0.351</v>
       </c>
       <c r="V3">
-        <v>0.1989655172413793</v>
+        <v>0.1063636363636364</v>
       </c>
       <c r="W3">
-        <v>0.1315334773218143</v>
+        <v>0.2377358490566038</v>
       </c>
       <c r="X3">
-        <v>0.2405668693711429</v>
+        <v>0.1869581906043234</v>
       </c>
       <c r="Y3">
-        <v>-0.1090333920493287</v>
+        <v>0.05077765845228033</v>
       </c>
       <c r="Z3">
-        <v>0.3177237700059277</v>
+        <v>0.9362072719355541</v>
       </c>
       <c r="AA3">
-        <v>0.09925384806469716</v>
+        <v>0.2690109531226448</v>
       </c>
       <c r="AB3">
-        <v>0.2013766261691633</v>
+        <v>0.1640054347011669</v>
       </c>
       <c r="AC3">
-        <v>-0.1021227781044661</v>
+        <v>0.105005518421478</v>
       </c>
       <c r="AD3">
-        <v>2.52</v>
+        <v>3.16</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.52</v>
+        <v>3.16</v>
       </c>
       <c r="AG3">
-        <v>1.943</v>
+        <v>2.809</v>
       </c>
       <c r="AH3">
-        <v>0.4649446494464945</v>
+        <v>0.4891640866873065</v>
       </c>
       <c r="AI3">
-        <v>0.4874274661508704</v>
+        <v>0.4450704225352113</v>
       </c>
       <c r="AJ3">
-        <v>0.4011976047904192</v>
+        <v>0.4598133900802095</v>
       </c>
       <c r="AK3">
-        <v>0.4230350533420423</v>
+        <v>0.4162098088605719</v>
       </c>
       <c r="AL3">
-        <v>0.367</v>
+        <v>1.03</v>
       </c>
       <c r="AM3">
-        <v>0.347</v>
+        <v>0.974</v>
       </c>
       <c r="AN3">
-        <v>1.75</v>
+        <v>1.385964912280702</v>
       </c>
       <c r="AO3">
-        <v>3.37874659400545</v>
+        <v>1.970873786407767</v>
       </c>
       <c r="AP3">
-        <v>1.349305555555556</v>
+        <v>1.232017543859649</v>
       </c>
       <c r="AQ3">
-        <v>3.573487031700288</v>
+        <v>2.084188911704312</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital Alliance PLC (COSE:CALT.N0000)</t>
+          <t>First Capital Treasuries PLC (COSE:FCT.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,6 +855,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.622</v>
+      </c>
+      <c r="E4">
+        <v>0.5770000000000001</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -868,82 +874,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.593</v>
+        <v>34.1</v>
       </c>
       <c r="L4">
-        <v>0.2837320574162679</v>
+        <v>0.4241293532338308</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>2.86</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0598326359832636</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.08387096774193548</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>2.86</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0598326359832636</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.08387096774193548</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.148</v>
+        <v>0.183</v>
       </c>
       <c r="V4">
-        <v>0.008314606741573033</v>
+        <v>0.003828451882845189</v>
       </c>
       <c r="W4">
-        <v>0.04900826446280992</v>
+        <v>2.706349206349207</v>
       </c>
       <c r="X4">
-        <v>0.3149280799441698</v>
+        <v>0.2953878151908034</v>
       </c>
       <c r="Y4">
-        <v>-0.2659198154813599</v>
+        <v>2.410961391158403</v>
       </c>
       <c r="Z4">
-        <v>0.1727272727272727</v>
+        <v>0.6461412349012706</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.2137963102512679</v>
+        <v>0.1814665386373609</v>
       </c>
       <c r="AC4">
-        <v>-0.2137963102512679</v>
+        <v>-0.1814665386373609</v>
       </c>
       <c r="AD4">
-        <v>29.8</v>
+        <v>125.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>29.8</v>
+        <v>125.3</v>
       </c>
       <c r="AG4">
-        <v>29.652</v>
+        <v>125.117</v>
       </c>
       <c r="AH4">
-        <v>0.6260504201680672</v>
+        <v>0.7238590410167534</v>
       </c>
       <c r="AI4">
-        <v>0.7813319349764027</v>
+        <v>0.7336065573770492</v>
       </c>
       <c r="AJ4">
-        <v>0.624884093399646</v>
+        <v>0.7235667979435221</v>
       </c>
       <c r="AK4">
-        <v>0.7804801010739102</v>
+        <v>0.7333208296945791</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First Capital Treasuries PLC (COSE:FCT.N0000)</t>
+          <t>Capital Alliance PLC (COSE:CALT.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -968,12 +977,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.135</v>
-      </c>
-      <c r="E5">
-        <v>0.111</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -987,82 +990,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2.37</v>
+        <v>47.5</v>
       </c>
       <c r="L5">
-        <v>0.1837209302325581</v>
+        <v>0.6634078212290503</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>3.1</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05730129390018485</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.06526315789473684</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>3.1</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05730129390018485</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.06526315789473684</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0.06900000000000001</v>
+        <v>0.283</v>
       </c>
       <c r="V5">
-        <v>0.001796875</v>
+        <v>0.005231053604436229</v>
       </c>
       <c r="W5">
-        <v>0.115609756097561</v>
+        <v>5.695443645083933</v>
       </c>
       <c r="X5">
-        <v>0.4294360183079588</v>
+        <v>0.2924792772647096</v>
       </c>
       <c r="Y5">
-        <v>-0.3138262622103978</v>
+        <v>5.402964367819223</v>
       </c>
       <c r="Z5">
-        <v>0.1513143232496217</v>
+        <v>1.884607285744367</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.226065939175459</v>
+        <v>0.1826569367760744</v>
       </c>
       <c r="AC5">
-        <v>-0.226065939175459</v>
+        <v>-0.1826569367760744</v>
       </c>
       <c r="AD5">
-        <v>111.9</v>
+        <v>139.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>111.9</v>
+        <v>139.4</v>
       </c>
       <c r="AG5">
-        <v>111.831</v>
+        <v>139.117</v>
       </c>
       <c r="AH5">
-        <v>0.7445109780439122</v>
+        <v>0.7204134366925065</v>
       </c>
       <c r="AI5">
-        <v>0.8987951807228917</v>
+        <v>0.7215320910973085</v>
       </c>
       <c r="AJ5">
-        <v>0.744393633803942</v>
+        <v>0.7200039334013053</v>
       </c>
       <c r="AK5">
-        <v>0.8987390602020398</v>
+        <v>0.7211235920110721</v>
       </c>
       <c r="AL5">
         <v>0</v>
